--- a/WGRDBESstockCoord/format/CEF_issues/effort_hawg_example.xlsx
+++ b/WGRDBESstockCoord/format/CEF_issues/effort_hawg_example.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{8E771CE0-C2AE-4677-869C-241D631D26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D78ED57-B1B3-4C99-AD9A-665889637FBA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0D78ED57-B1B3-4C99-AD9A-665889637FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="areas" sheetId="6" r:id="rId1"/>
